--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -70,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -84,6 +84,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,8 +504,6 @@
       <c r="D2" t="n">
         <v>1288</v>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -517,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1289"/>
+  <dimension ref="A1:N1290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27238,6 +27237,14 @@
         <v>25</v>
       </c>
     </row>
+    <row r="1290">
+      <c r="A1290" s="5" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1290" t="n">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1290"/>
+  <dimension ref="A1:O1291"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27253,6 +27253,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1291">
+      <c r="A1291" s="5" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1291" t="n">
+        <v>25</v>
+      </c>
+      <c r="C1291" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1291"/>
+  <dimension ref="A1:O1292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27264,6 +27264,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1292">
+      <c r="A1292" s="5" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1292" t="n">
+        <v>25</v>
+      </c>
+      <c r="C1292" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1292"/>
+  <dimension ref="A1:O1293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27275,6 +27275,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1293">
+      <c r="A1293" s="5" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1293" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C1293" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1293"/>
+  <dimension ref="A1:O1294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27286,6 +27286,17 @@
         <v>2.5</v>
       </c>
     </row>
+    <row r="1294">
+      <c r="A1294" s="5" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1294" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C1294" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1294"/>
+  <dimension ref="A1:O1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27297,6 +27297,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1295">
+      <c r="A1295" s="5" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1295" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C1295" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1295"/>
+  <dimension ref="A1:O1296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27308,6 +27308,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1296">
+      <c r="A1296" s="5" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1296" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C1296" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
+++ b/玉米大豆历史数据/玉米基差/Wyoming Basis.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O1296"/>
+  <dimension ref="A1:O1297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -27319,6 +27319,17 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1297">
+      <c r="A1297" s="5" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1297" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="C1297" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
